--- a/AAII_Financials/Quarterly/PRFX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PRFX_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="92">
   <si>
     <t>PRFX</t>
   </si>
@@ -656,98 +656,105 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43830</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43646</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43465</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43281</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -805,8 +812,14 @@
       <c r="U8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -864,8 +877,14 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -923,8 +942,14 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -946,67 +971,75 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E12" s="3">
+        <v>600</v>
+      </c>
+      <c r="F12" s="3">
         <v>1200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>1500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>1900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>1100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>1000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>100</v>
       </c>
-      <c r="O12" s="3">
-        <v>0</v>
-      </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
+        <v>0</v>
+      </c>
+      <c r="R12" s="3">
         <v>200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>100</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1064,8 +1097,14 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1123,8 +1162,14 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1182,8 +1227,14 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1202,67 +1253,75 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F17" s="3">
         <v>2300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>2400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>3300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>2100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1700</v>
-      </c>
-      <c r="J17" s="3">
-        <v>1700</v>
-      </c>
-      <c r="K17" s="3">
-        <v>1800</v>
       </c>
       <c r="L17" s="3">
         <v>1700</v>
       </c>
       <c r="M17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="N17" s="3">
+        <v>1700</v>
+      </c>
+      <c r="O17" s="3">
         <v>2000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>300</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1270,58 +1329,64 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="G18" s="3">
         <v>-2400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-3300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-2100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-1800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-1700</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-1800</v>
       </c>
       <c r="L18" s="3">
         <v>-1700</v>
       </c>
       <c r="M18" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="O18" s="3">
         <v>-2000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-300</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1343,8 +1408,10 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1352,16 +1419,16 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
-        <v>100</v>
+        <v>1400</v>
       </c>
       <c r="F20" s="3">
         <v>100</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I20" s="3">
         <v>0</v>
@@ -1379,22 +1446,22 @@
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-600</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-300</v>
       </c>
       <c r="Q20" s="3">
         <v>-200</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
+      <c r="R20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="S20" s="3">
+        <v>-200</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
@@ -1402,8 +1469,14 @@
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1411,38 +1484,38 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="G21" s="3">
         <v>-2300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-3200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-2100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-1800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-1700</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-1800</v>
       </c>
       <c r="L21" s="3">
         <v>-1700</v>
       </c>
       <c r="M21" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="N21" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="O21" s="3">
         <v>-2000</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1461,8 +1534,14 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1520,58 +1599,64 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3">
         <v>-2200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-2300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-3200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-2100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-1800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-1700</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-1800</v>
       </c>
       <c r="L23" s="3">
         <v>-1700</v>
       </c>
       <c r="M23" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="N23" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="O23" s="3">
         <v>-2000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-1300</v>
-      </c>
-      <c r="O23" s="3">
-        <v>-400</v>
-      </c>
-      <c r="P23" s="3">
-        <v>-800</v>
       </c>
       <c r="Q23" s="3">
         <v>-400</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
+      <c r="R23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="S23" s="3">
+        <v>-400</v>
       </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
@@ -1579,37 +1664,43 @@
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3">
+        <v>0</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
+      <c r="H24" s="3">
+        <v>0</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
+      <c r="L24" s="3">
+        <v>0</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
@@ -1623,11 +1714,11 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
-      <c r="R24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S24" s="3">
         <v>0</v>
@@ -1638,8 +1729,14 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1697,58 +1794,64 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
         <v>-2200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-2300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-3200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-2100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-1800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-1700</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-1800</v>
       </c>
       <c r="L26" s="3">
         <v>-1700</v>
       </c>
       <c r="M26" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="N26" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="O26" s="3">
         <v>-2000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-1300</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-400</v>
-      </c>
-      <c r="P26" s="3">
-        <v>-800</v>
       </c>
       <c r="Q26" s="3">
         <v>-400</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
+      <c r="R26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="S26" s="3">
+        <v>-400</v>
       </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
@@ -1756,67 +1859,79 @@
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
         <v>-2200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-2300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-3200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-2100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-1800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-1700</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-1800</v>
       </c>
       <c r="L27" s="3">
         <v>-1700</v>
       </c>
       <c r="M27" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="N27" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="O27" s="3">
         <v>-2000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-2400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-1000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-900</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1874,8 +1989,14 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1933,8 +2054,14 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1992,8 +2119,14 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2051,8 +2184,14 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2060,16 +2199,16 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
-        <v>-100</v>
+        <v>-1400</v>
       </c>
       <c r="F32" s="3">
         <v>-100</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I32" s="3">
         <v>0</v>
@@ -2087,22 +2226,22 @@
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>600</v>
-      </c>
-      <c r="O32" s="3">
-        <v>200</v>
-      </c>
-      <c r="P32" s="3">
-        <v>300</v>
       </c>
       <c r="Q32" s="3">
         <v>200</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
+      <c r="R32" s="3">
+        <v>300</v>
+      </c>
+      <c r="S32" s="3">
+        <v>200</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
@@ -2110,67 +2249,79 @@
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E33" s="3">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3">
         <v>-2200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-2300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-3200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-2100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-1800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-1700</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-1800</v>
       </c>
       <c r="L33" s="3">
         <v>-1700</v>
       </c>
       <c r="M33" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="N33" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="O33" s="3">
         <v>-2000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-2400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-1000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-900</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2228,131 +2379,149 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3">
         <v>-2200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-2300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-3200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-2100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-1800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-1700</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-1800</v>
       </c>
       <c r="L35" s="3">
         <v>-1700</v>
       </c>
       <c r="M35" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="N35" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="O35" s="3">
         <v>-2000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-2400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-1000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-900</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43830</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43646</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43465</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43281</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2374,8 +2543,10 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2397,53 +2568,55 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>7600</v>
+      </c>
+      <c r="F41" s="3">
         <v>5100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>8100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>4100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>6900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>13800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>15400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>16500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>18300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>17800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>19400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>100</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2456,8 +2629,14 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2515,8 +2694,14 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2574,8 +2759,14 @@
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2633,52 +2824,58 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E45" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F45" s="3">
         <v>3100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>2200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>8200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>7900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>2100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>2200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>2500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>2000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>2000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1900</v>
       </c>
-      <c r="N45" s="3">
-        <v>0</v>
-      </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>0</v>
       </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
@@ -2692,53 +2889,59 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>10700</v>
+      </c>
+      <c r="F46" s="3">
         <v>8300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>10400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>12300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>14800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>15900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>17700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>19000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>20300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>19800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>21300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>100</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2751,8 +2954,14 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2810,16 +3019,22 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F48" s="3">
         <v>0</v>
@@ -2828,25 +3043,25 @@
         <v>0</v>
       </c>
       <c r="H48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3">
         <v>100</v>
       </c>
       <c r="K48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
+      <c r="N48" s="3">
+        <v>0</v>
       </c>
       <c r="O48" s="3">
         <v>0</v>
@@ -2854,8 +3069,8 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
+      <c r="Q48" s="3">
+        <v>0</v>
       </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
@@ -2869,8 +3084,14 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2928,8 +3149,14 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2987,8 +3214,14 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3046,8 +3279,14 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3075,21 +3314,21 @@
       <c r="K52" s="3">
         <v>0</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N52" s="3">
+      <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3">
         <v>200</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3105,8 +3344,14 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3164,53 +3409,59 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>10900</v>
+      </c>
+      <c r="F54" s="3">
         <v>8300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>10400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>12300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>14900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>16000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>17700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>19100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>20300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>19800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>21400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>100</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3223,8 +3474,14 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3246,8 +3503,10 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3269,34 +3528,36 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>200</v>
+      </c>
+      <c r="F57" s="3">
         <v>100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>300</v>
-      </c>
-      <c r="F57" s="3">
-        <v>200</v>
-      </c>
-      <c r="G57" s="3">
-        <v>400</v>
       </c>
       <c r="H57" s="3">
         <v>200</v>
       </c>
       <c r="I57" s="3">
+        <v>400</v>
+      </c>
+      <c r="J57" s="3">
+        <v>200</v>
+      </c>
+      <c r="K57" s="3">
         <v>300</v>
-      </c>
-      <c r="J57" s="3">
-        <v>100</v>
-      </c>
-      <c r="K57" s="3">
-        <v>200</v>
       </c>
       <c r="L57" s="3">
         <v>100</v>
@@ -3304,11 +3565,11 @@
       <c r="M57" s="3">
         <v>200</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
+      <c r="N57" s="3">
+        <v>100</v>
+      </c>
+      <c r="O57" s="3">
+        <v>200</v>
       </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
@@ -3322,14 +3583,20 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T57" s="3">
-        <v>0</v>
-      </c>
-      <c r="U57" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V57" s="3">
+        <v>0</v>
+      </c>
+      <c r="W57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3357,21 +3624,21 @@
       <c r="K58" s="3">
         <v>0</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N58" s="3">
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3">
         <v>6200</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3387,52 +3654,58 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>900</v>
+      </c>
+      <c r="F59" s="3">
         <v>1000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>400</v>
-      </c>
-      <c r="J59" s="3">
-        <v>600</v>
-      </c>
-      <c r="K59" s="3">
-        <v>500</v>
       </c>
       <c r="L59" s="3">
         <v>600</v>
       </c>
       <c r="M59" s="3">
+        <v>500</v>
+      </c>
+      <c r="N59" s="3">
         <v>600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
+        <v>600</v>
+      </c>
+      <c r="P59" s="3">
         <v>200</v>
       </c>
-      <c r="O59" s="3">
-        <v>0</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
+      <c r="Q59" s="3">
+        <v>0</v>
       </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
@@ -3446,52 +3719,58 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E60" s="3">
         <v>1100</v>
-      </c>
-      <c r="E60" s="3">
-        <v>1300</v>
       </c>
       <c r="F60" s="3">
         <v>1100</v>
       </c>
       <c r="G60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H60" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I60" s="3">
         <v>1200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>6300</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
+      <c r="Q60" s="3">
+        <v>0</v>
       </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
@@ -3505,8 +3784,14 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3544,14 +3829,14 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>4900</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3564,16 +3849,22 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E62" s="3">
-        <v>200</v>
+        <v>1200</v>
       </c>
       <c r="F62" s="3">
         <v>200</v>
@@ -3600,14 +3891,14 @@
         <v>200</v>
       </c>
       <c r="N62" s="3">
+        <v>200</v>
+      </c>
+      <c r="O62" s="3">
+        <v>200</v>
+      </c>
+      <c r="P62" s="3">
         <v>400</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3623,8 +3914,14 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3682,8 +3979,14 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3741,8 +4044,14 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3800,53 +4109,59 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1300</v>
+        <v>2700</v>
       </c>
       <c r="E66" s="3">
-        <v>1500</v>
+        <v>2200</v>
       </c>
       <c r="F66" s="3">
         <v>1300</v>
       </c>
       <c r="G66" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I66" s="3">
         <v>1400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>6800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>5000</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3859,8 +4174,14 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3882,8 +4203,10 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3941,8 +4264,14 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4000,8 +4329,14 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4036,17 +4371,17 @@
         <v>0</v>
       </c>
       <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
         <v>6600</v>
       </c>
-      <c r="O70" s="3">
+      <c r="Q70" s="3">
         <v>6600</v>
       </c>
-      <c r="P70" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q70" s="3">
-        <v>0</v>
-      </c>
       <c r="R70" s="3">
         <v>0</v>
       </c>
@@ -4059,8 +4394,14 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4118,53 +4459,59 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-41900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-37000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
+        <v>-37000</v>
+      </c>
+      <c r="G72" s="3">
         <v>-34800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-32500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-29400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-27200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-25400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-23700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-22000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-20200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-18500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-12400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-11600</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4177,8 +4524,14 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4236,8 +4589,14 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4295,8 +4654,14 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4354,53 +4719,59 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>8600</v>
+      </c>
+      <c r="F76" s="3">
         <v>7000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>8900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>11000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>13400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>15200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>16700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>18100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>19500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>19000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>20400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>-12200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>-11500</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4413,8 +4784,14 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4472,131 +4849,149 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43830</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43646</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43465</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43281</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E81" s="3">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3">
         <v>-2200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-2300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-3200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-2100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-1800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-1700</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-1800</v>
       </c>
       <c r="L81" s="3">
         <v>-1700</v>
       </c>
       <c r="M81" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="N81" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="O81" s="3">
         <v>-2000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-2400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-1000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-900</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4618,8 +5013,10 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4653,11 +5050,11 @@
       <c r="M83" s="3">
         <v>0</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3">
+        <v>0</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
@@ -4671,14 +5068,20 @@
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
-      </c>
-      <c r="U83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4736,8 +5139,14 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4795,8 +5204,14 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4854,8 +5269,14 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4913,8 +5334,14 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4972,53 +5399,59 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F89" s="3">
         <v>-2000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-2000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-2900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-1800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-1600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-1800</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-200</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5031,8 +5464,14 @@
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5054,8 +5493,10 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5089,11 +5530,11 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
@@ -5107,14 +5548,20 @@
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5172,8 +5619,14 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5231,29 +5684,35 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>6000</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>-6000</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
         <v>0</v>
       </c>
@@ -5266,8 +5725,8 @@
       <c r="M94" s="3">
         <v>0</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
+      <c r="N94" s="3">
+        <v>0</v>
       </c>
       <c r="O94" s="3">
         <v>0</v>
@@ -5275,8 +5734,8 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
+      <c r="Q94" s="3">
+        <v>0</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
@@ -5284,14 +5743,20 @@
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5313,8 +5778,10 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5372,8 +5839,14 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5431,8 +5904,14 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5490,8 +5969,14 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5549,13 +6034,19 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3">
+        <v>1000</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>3</v>
@@ -5572,30 +6063,30 @@
       <c r="I100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>1900</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>5600</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3">
         <v>200</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5608,8 +6099,14 @@
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5619,17 +6116,17 @@
       <c r="E101" s="3">
         <v>0</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
@@ -5637,8 +6134,8 @@
       <c r="K101" s="3">
         <v>0</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -5667,52 +6164,58 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F102" s="3">
         <v>-3000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>4000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-2800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-6900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-1600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-1100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-1800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-1600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>3700</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
+      <c r="Q102" s="3">
+        <v>0</v>
       </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
@@ -5724,6 +6227,12 @@
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PRFX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PRFX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="92">
   <si>
     <t>PRFX</t>
   </si>
@@ -656,94 +656,95 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43830</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43646</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43465</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43281</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
@@ -753,8 +754,11 @@
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -818,8 +822,11 @@
       <c r="W8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -883,8 +890,11 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -948,8 +958,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -973,62 +986,63 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E12" s="3">
         <v>2700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1100</v>
-      </c>
-      <c r="J12" s="3">
-        <v>700</v>
       </c>
       <c r="K12" s="3">
         <v>700</v>
       </c>
       <c r="L12" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="M12" s="3">
         <v>600</v>
       </c>
       <c r="N12" s="3">
+        <v>600</v>
+      </c>
+      <c r="O12" s="3">
         <v>700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>100</v>
       </c>
-      <c r="Q12" s="3">
-        <v>0</v>
-      </c>
       <c r="R12" s="3">
+        <v>0</v>
+      </c>
+      <c r="S12" s="3">
         <v>200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>100</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1038,8 +1052,11 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1103,8 +1120,11 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1168,8 +1188,11 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1233,8 +1256,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1255,62 +1281,63 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E17" s="3">
         <v>3600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1800</v>
-      </c>
-      <c r="K17" s="3">
-        <v>1700</v>
       </c>
       <c r="L17" s="3">
         <v>1700</v>
       </c>
       <c r="M17" s="3">
+        <v>1700</v>
+      </c>
+      <c r="N17" s="3">
         <v>1800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>300</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1320,8 +1347,11 @@
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1329,53 +1359,53 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-3300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1800</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-1700</v>
       </c>
       <c r="L18" s="3">
         <v>-1700</v>
       </c>
       <c r="M18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="N18" s="3">
         <v>-1800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-300</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1385,8 +1415,11 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1410,8 +1443,9 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1419,10 +1453,10 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F20" s="3">
         <v>1400</v>
-      </c>
-      <c r="F20" s="3">
-        <v>100</v>
       </c>
       <c r="G20" s="3">
         <v>100</v>
@@ -1431,7 +1465,7 @@
         <v>100</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
@@ -1452,20 +1486,20 @@
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-200</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1475,8 +1509,11 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1484,41 +1521,41 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
-        <v>0</v>
+        <v>-4900</v>
       </c>
       <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
         <v>-2200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-3200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1800</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-1700</v>
       </c>
       <c r="L21" s="3">
         <v>-1700</v>
       </c>
       <c r="M21" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="N21" s="3">
         <v>-1800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2000</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1540,8 +1577,11 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1605,62 +1645,65 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4900</v>
       </c>
-      <c r="E23" s="3">
-        <v>0</v>
-      </c>
       <c r="F23" s="3">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3">
         <v>-2200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1800</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-1700</v>
       </c>
       <c r="L23" s="3">
         <v>-1700</v>
       </c>
       <c r="M23" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="N23" s="3">
         <v>-1800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-400</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1670,16 +1713,19 @@
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>3</v>
@@ -1687,11 +1733,11 @@
       <c r="G24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
@@ -1699,11 +1745,11 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
@@ -1720,8 +1766,8 @@
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
+      <c r="S24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T24" s="3">
         <v>0</v>
@@ -1735,8 +1781,11 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1800,62 +1849,65 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4900</v>
       </c>
-      <c r="E26" s="3">
-        <v>0</v>
-      </c>
       <c r="F26" s="3">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3">
         <v>-2200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1800</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-1700</v>
       </c>
       <c r="L26" s="3">
         <v>-1700</v>
       </c>
       <c r="M26" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="N26" s="3">
         <v>-1800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-400</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1865,62 +1917,65 @@
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4900</v>
       </c>
-      <c r="E27" s="3">
-        <v>0</v>
-      </c>
       <c r="F27" s="3">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3">
         <v>-2200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1800</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-1700</v>
       </c>
       <c r="L27" s="3">
         <v>-1700</v>
       </c>
       <c r="M27" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="N27" s="3">
         <v>-1800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-900</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1930,8 +1985,11 @@
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1995,8 +2053,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2060,8 +2121,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2125,8 +2189,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2190,8 +2257,11 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2199,10 +2269,10 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1400</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-100</v>
       </c>
       <c r="G32" s="3">
         <v>-100</v>
@@ -2211,7 +2281,7 @@
         <v>-100</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
@@ -2232,20 +2302,20 @@
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>200</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2255,62 +2325,65 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4900</v>
       </c>
-      <c r="E33" s="3">
-        <v>0</v>
-      </c>
       <c r="F33" s="3">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3">
         <v>-2200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1800</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-1700</v>
       </c>
       <c r="L33" s="3">
         <v>-1700</v>
       </c>
       <c r="M33" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="N33" s="3">
         <v>-1800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-900</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2320,8 +2393,11 @@
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2385,62 +2461,65 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4900</v>
       </c>
-      <c r="E35" s="3">
-        <v>0</v>
-      </c>
       <c r="F35" s="3">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3">
         <v>-2200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1800</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-1700</v>
       </c>
       <c r="L35" s="3">
         <v>-1700</v>
       </c>
       <c r="M35" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="N35" s="3">
         <v>-1800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-900</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2450,67 +2529,70 @@
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43830</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43646</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43465</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43281</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2520,8 +2602,11 @@
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2545,8 +2630,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2570,56 +2656,57 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E41" s="3">
         <v>8000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>13800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>15400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>16500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>18300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>17800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>19400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>100</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2635,8 +2722,11 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2700,8 +2790,11 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2765,8 +2858,11 @@
       <c r="W43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2830,55 +2926,58 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>900</v>
+      </c>
+      <c r="E45" s="3">
         <v>1800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>8200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2500</v>
-      </c>
-      <c r="M45" s="3">
-        <v>2000</v>
       </c>
       <c r="N45" s="3">
         <v>2000</v>
       </c>
       <c r="O45" s="3">
+        <v>2000</v>
+      </c>
+      <c r="P45" s="3">
         <v>1900</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3">
         <v>0</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
+      <c r="R45" s="3">
+        <v>0</v>
       </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
@@ -2895,56 +2994,59 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E46" s="3">
         <v>9800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>10700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>14800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>15900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>17700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>19000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>20300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>19800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>21300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>100</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2960,8 +3062,11 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3025,8 +3130,11 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3037,7 +3145,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G48" s="3">
         <v>0</v>
@@ -3049,7 +3157,7 @@
         <v>0</v>
       </c>
       <c r="J48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3">
         <v>100</v>
@@ -3058,7 +3166,7 @@
         <v>100</v>
       </c>
       <c r="M48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N48" s="3">
         <v>0</v>
@@ -3066,14 +3174,14 @@
       <c r="O48" s="3">
         <v>0</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>0</v>
-      </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
+      <c r="P48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3">
+        <v>0</v>
       </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
@@ -3090,8 +3198,11 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3155,8 +3266,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3220,8 +3334,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3285,8 +3402,11 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3320,18 +3440,18 @@
       <c r="M52" s="3">
         <v>0</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
+      <c r="N52" s="3">
+        <v>0</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3">
         <v>200</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3350,8 +3470,11 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3415,56 +3538,59 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E54" s="3">
         <v>9900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>12300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>14900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>16000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>17700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>19100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>20300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>19800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>21400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>100</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3480,8 +3606,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3505,8 +3634,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3530,8 +3660,9 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3542,38 +3673,38 @@
         <v>200</v>
       </c>
       <c r="F57" s="3">
+        <v>200</v>
+      </c>
+      <c r="G57" s="3">
         <v>100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>200</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3589,14 +3720,17 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V57" s="3">
-        <v>0</v>
+      <c r="V57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3630,18 +3764,18 @@
       <c r="M58" s="3">
         <v>0</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
+      <c r="N58" s="3">
+        <v>0</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P58" s="3">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3">
         <v>6200</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3660,55 +3794,58 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>900</v>
-      </c>
-      <c r="F59" s="3">
-        <v>1000</v>
       </c>
       <c r="G59" s="3">
         <v>1000</v>
       </c>
       <c r="H59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I59" s="3">
         <v>900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>500</v>
-      </c>
-      <c r="N59" s="3">
-        <v>600</v>
       </c>
       <c r="O59" s="3">
         <v>600</v>
       </c>
       <c r="P59" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q59" s="3">
         <v>200</v>
       </c>
-      <c r="Q59" s="3">
-        <v>0</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
+      <c r="R59" s="3">
+        <v>0</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
@@ -3725,55 +3862,58 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E60" s="3">
         <v>2400</v>
-      </c>
-      <c r="E60" s="3">
-        <v>1100</v>
       </c>
       <c r="F60" s="3">
         <v>1100</v>
       </c>
       <c r="G60" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H60" s="3">
         <v>1300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>500</v>
-      </c>
-      <c r="K60" s="3">
-        <v>800</v>
       </c>
       <c r="L60" s="3">
         <v>800</v>
       </c>
       <c r="M60" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="N60" s="3">
         <v>600</v>
       </c>
       <c r="O60" s="3">
+        <v>600</v>
+      </c>
+      <c r="P60" s="3">
         <v>700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6300</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
+      <c r="R60" s="3">
+        <v>0</v>
       </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
@@ -3790,8 +3930,11 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3835,11 +3978,11 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>4900</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3855,8 +3998,11 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3864,10 +4010,10 @@
         <v>300</v>
       </c>
       <c r="E62" s="3">
+        <v>300</v>
+      </c>
+      <c r="F62" s="3">
         <v>1200</v>
-      </c>
-      <c r="F62" s="3">
-        <v>200</v>
       </c>
       <c r="G62" s="3">
         <v>200</v>
@@ -3897,11 +4043,11 @@
         <v>200</v>
       </c>
       <c r="P62" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q62" s="3">
         <v>400</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3920,8 +4066,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3985,8 +4134,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4050,8 +4202,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4115,56 +4270,59 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E66" s="3">
         <v>2700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>800</v>
-      </c>
-      <c r="K66" s="3">
-        <v>1000</v>
       </c>
       <c r="L66" s="3">
         <v>1000</v>
       </c>
       <c r="M66" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N66" s="3">
         <v>900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5000</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4180,8 +4338,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4205,8 +4366,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4270,8 +4432,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4335,8 +4500,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4377,13 +4545,13 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
-        <v>6600</v>
+        <v>0</v>
       </c>
       <c r="Q70" s="3">
         <v>6600</v>
       </c>
       <c r="R70" s="3">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="S70" s="3">
         <v>0</v>
@@ -4400,8 +4568,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4465,56 +4636,59 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-47400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-41900</v>
-      </c>
-      <c r="E72" s="3">
-        <v>-37000</v>
       </c>
       <c r="F72" s="3">
         <v>-37000</v>
       </c>
       <c r="G72" s="3">
+        <v>-37000</v>
+      </c>
+      <c r="H72" s="3">
         <v>-34800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-32500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-29400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-27200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-25400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-23700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-22000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-20200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-18500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-12400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-11600</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4530,8 +4704,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4595,8 +4772,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4660,8 +4840,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4725,56 +4908,59 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E76" s="3">
         <v>7200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>15200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>16700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>18100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>19500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>20400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-12200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-11500</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4790,8 +4976,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4855,67 +5044,70 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43830</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43646</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43465</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43281</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4925,62 +5117,65 @@
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4900</v>
       </c>
-      <c r="E81" s="3">
-        <v>0</v>
-      </c>
       <c r="F81" s="3">
+        <v>0</v>
+      </c>
+      <c r="G81" s="3">
         <v>-2200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1800</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-1700</v>
       </c>
       <c r="L81" s="3">
         <v>-1700</v>
       </c>
       <c r="M81" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="N81" s="3">
         <v>-1800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-900</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4990,8 +5185,11 @@
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5015,8 +5213,9 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5056,8 +5255,8 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
+      <c r="P83" s="3">
+        <v>0</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
@@ -5074,14 +5273,17 @@
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V83" s="3">
-        <v>0</v>
+      <c r="V83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5145,8 +5347,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5210,8 +5415,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5275,8 +5483,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5340,8 +5551,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5405,56 +5619,59 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1200</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-2000</v>
       </c>
       <c r="G89" s="3">
         <v>-2000</v>
       </c>
       <c r="H89" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="I89" s="3">
         <v>-2900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1800</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3">
         <v>-200</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5470,8 +5687,11 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5495,8 +5715,9 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5536,8 +5757,8 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
@@ -5554,14 +5775,17 @@
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5625,8 +5849,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5690,32 +5917,35 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>1000</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-1000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>6000</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-6000</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
         <v>0</v>
       </c>
@@ -5731,14 +5961,14 @@
       <c r="O94" s="3">
         <v>0</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
@@ -5749,14 +5979,17 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
+      <c r="V94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5780,8 +6013,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5845,8 +6079,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5910,8 +6147,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5975,8 +6215,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6040,17 +6283,20 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3">
         <v>1000</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6069,27 +6315,27 @@
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>1900</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>5600</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3">
         <v>200</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6105,13 +6351,16 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E101" s="3">
         <v>0</v>
@@ -6122,8 +6371,8 @@
       <c r="G101" s="3">
         <v>0</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
+      <c r="H101" s="3">
+        <v>0</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>3</v>
@@ -6131,14 +6380,14 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -6170,55 +6419,58 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E102" s="3">
         <v>500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>4000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-6900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3700</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3">
+        <v>0</v>
       </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
@@ -6233,6 +6485,9 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PRFX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PRFX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="92">
   <si>
     <t>PRFX</t>
   </si>
@@ -656,98 +656,99 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43830</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43646</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43465</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43281</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
@@ -757,8 +758,11 @@
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -825,8 +829,11 @@
       <c r="X8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -893,8 +900,11 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -961,8 +971,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -987,65 +1000,66 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E12" s="3">
         <v>4700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1100</v>
-      </c>
-      <c r="K12" s="3">
-        <v>700</v>
       </c>
       <c r="L12" s="3">
         <v>700</v>
       </c>
       <c r="M12" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="N12" s="3">
         <v>600</v>
       </c>
       <c r="O12" s="3">
+        <v>600</v>
+      </c>
+      <c r="P12" s="3">
         <v>700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>100</v>
       </c>
-      <c r="R12" s="3">
-        <v>0</v>
-      </c>
       <c r="S12" s="3">
+        <v>0</v>
+      </c>
+      <c r="T12" s="3">
         <v>200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>100</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1055,8 +1069,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1123,8 +1140,11 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1191,8 +1211,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1259,8 +1282,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1282,65 +1308,66 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E17" s="3">
         <v>5600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1800</v>
-      </c>
-      <c r="L17" s="3">
-        <v>1700</v>
       </c>
       <c r="M17" s="3">
         <v>1700</v>
       </c>
       <c r="N17" s="3">
+        <v>1700</v>
+      </c>
+      <c r="O17" s="3">
         <v>1800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>300</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1350,8 +1377,11 @@
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1359,56 +1389,56 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="F18" s="3">
         <v>-3600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-3300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1800</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-1700</v>
       </c>
       <c r="M18" s="3">
         <v>-1700</v>
       </c>
       <c r="N18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="O18" s="3">
         <v>-1800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-300</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1418,8 +1448,11 @@
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1444,8 +1477,9 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1453,13 +1487,13 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>100</v>
+      </c>
+      <c r="F20" s="3">
         <v>-1300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1400</v>
-      </c>
-      <c r="G20" s="3">
-        <v>100</v>
       </c>
       <c r="H20" s="3">
         <v>100</v>
@@ -1468,7 +1502,7 @@
         <v>100</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1489,20 +1523,20 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-200</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1512,8 +1546,11 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1521,44 +1558,44 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="F21" s="3">
         <v>-4900</v>
       </c>
-      <c r="F21" s="3">
-        <v>0</v>
-      </c>
       <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
         <v>-2200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-2300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-3200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1800</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-1700</v>
       </c>
       <c r="M21" s="3">
         <v>-1700</v>
       </c>
       <c r="N21" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="O21" s="3">
         <v>-1800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1580,8 +1617,11 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1648,65 +1688,68 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-4900</v>
       </c>
-      <c r="F23" s="3">
-        <v>0</v>
-      </c>
       <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
         <v>-2200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1800</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-1700</v>
       </c>
       <c r="M23" s="3">
         <v>-1700</v>
       </c>
       <c r="N23" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="O23" s="3">
         <v>-1800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-400</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1716,19 +1759,22 @@
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
@@ -1736,11 +1782,11 @@
       <c r="H24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
@@ -1748,11 +1794,11 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
@@ -1769,8 +1815,8 @@
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
+      <c r="T24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
@@ -1784,8 +1830,11 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1852,65 +1901,68 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-4900</v>
       </c>
-      <c r="F26" s="3">
-        <v>0</v>
-      </c>
       <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
         <v>-2200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1800</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-1700</v>
       </c>
       <c r="M26" s="3">
         <v>-1700</v>
       </c>
       <c r="N26" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="O26" s="3">
         <v>-1800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-400</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1920,65 +1972,68 @@
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-4900</v>
       </c>
-      <c r="F27" s="3">
-        <v>0</v>
-      </c>
       <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
         <v>-2200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1800</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-1700</v>
       </c>
       <c r="M27" s="3">
         <v>-1700</v>
       </c>
       <c r="N27" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="O27" s="3">
         <v>-1800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-900</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1988,8 +2043,11 @@
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2056,8 +2114,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2124,8 +2185,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2192,8 +2256,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2260,8 +2327,11 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2269,13 +2339,13 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F32" s="3">
         <v>1300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1400</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-100</v>
       </c>
       <c r="H32" s="3">
         <v>-100</v>
@@ -2284,7 +2354,7 @@
         <v>-100</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -2305,20 +2375,20 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>200</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2328,65 +2398,68 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-4900</v>
       </c>
-      <c r="F33" s="3">
-        <v>0</v>
-      </c>
       <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3">
         <v>-2200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1800</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-1700</v>
       </c>
       <c r="M33" s="3">
         <v>-1700</v>
       </c>
       <c r="N33" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="O33" s="3">
         <v>-1800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-900</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2396,8 +2469,11 @@
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2464,65 +2540,68 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-4900</v>
       </c>
-      <c r="F35" s="3">
-        <v>0</v>
-      </c>
       <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
         <v>-2200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1800</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-1700</v>
       </c>
       <c r="M35" s="3">
         <v>-1700</v>
       </c>
       <c r="N35" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="O35" s="3">
         <v>-1800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-900</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2532,70 +2611,73 @@
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43830</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43646</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43465</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43281</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2605,8 +2687,11 @@
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2631,8 +2716,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2657,59 +2743,60 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E41" s="3">
         <v>4300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>13800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>15400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>16500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>18300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>17800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>19400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>100</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2725,8 +2812,11 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2793,8 +2883,11 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2861,8 +2954,11 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2929,58 +3025,61 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>200</v>
+      </c>
+      <c r="E45" s="3">
         <v>900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>8200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2500</v>
-      </c>
-      <c r="N45" s="3">
-        <v>2000</v>
       </c>
       <c r="O45" s="3">
         <v>2000</v>
       </c>
       <c r="P45" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Q45" s="3">
         <v>1900</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
+      <c r="S45" s="3">
+        <v>0</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
@@ -2997,59 +3096,62 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E46" s="3">
         <v>5200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>10700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>10400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>12300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>14800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>15900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>17700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>19000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>20300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>19800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>21300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>100</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3065,8 +3167,11 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3133,8 +3238,11 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3148,7 +3256,7 @@
         <v>100</v>
       </c>
       <c r="G48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H48" s="3">
         <v>0</v>
@@ -3160,7 +3268,7 @@
         <v>0</v>
       </c>
       <c r="K48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3">
         <v>100</v>
@@ -3169,7 +3277,7 @@
         <v>100</v>
       </c>
       <c r="N48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O48" s="3">
         <v>0</v>
@@ -3177,14 +3285,14 @@
       <c r="P48" s="3">
         <v>0</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R48" s="3">
-        <v>0</v>
-      </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S48" s="3">
+        <v>0</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
@@ -3201,8 +3309,11 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3269,8 +3380,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3337,8 +3451,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3405,8 +3522,11 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3443,18 +3563,18 @@
       <c r="N52" s="3">
         <v>0</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
+      <c r="O52" s="3">
+        <v>0</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3">
         <v>200</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3473,8 +3593,11 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3541,59 +3664,62 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E54" s="3">
         <v>5400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>12300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>14900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>16000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>17700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>19100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>20300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>19800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>21400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>100</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3609,8 +3735,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3635,8 +3764,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3661,13 +3791,14 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E57" s="3">
         <v>200</v>
@@ -3676,38 +3807,38 @@
         <v>200</v>
       </c>
       <c r="G57" s="3">
+        <v>200</v>
+      </c>
+      <c r="H57" s="3">
         <v>100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>200</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3723,14 +3854,17 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W57" s="3">
-        <v>0</v>
+      <c r="W57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3767,18 +3901,18 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
+      <c r="O58" s="3">
+        <v>0</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3">
         <v>6200</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3797,58 +3931,61 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E59" s="3">
         <v>3000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>900</v>
-      </c>
-      <c r="G59" s="3">
-        <v>1000</v>
       </c>
       <c r="H59" s="3">
         <v>1000</v>
       </c>
       <c r="I59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J59" s="3">
         <v>900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>500</v>
-      </c>
-      <c r="O59" s="3">
-        <v>600</v>
       </c>
       <c r="P59" s="3">
         <v>600</v>
       </c>
       <c r="Q59" s="3">
+        <v>600</v>
+      </c>
+      <c r="R59" s="3">
         <v>200</v>
       </c>
-      <c r="R59" s="3">
-        <v>0</v>
-      </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
+      <c r="S59" s="3">
+        <v>0</v>
       </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
@@ -3865,58 +4002,61 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E60" s="3">
         <v>3300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2400</v>
-      </c>
-      <c r="F60" s="3">
-        <v>1100</v>
       </c>
       <c r="G60" s="3">
         <v>1100</v>
       </c>
       <c r="H60" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I60" s="3">
         <v>1300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>500</v>
-      </c>
-      <c r="L60" s="3">
-        <v>800</v>
       </c>
       <c r="M60" s="3">
         <v>800</v>
       </c>
       <c r="N60" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="O60" s="3">
         <v>600</v>
       </c>
       <c r="P60" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q60" s="3">
         <v>700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6300</v>
       </c>
-      <c r="R60" s="3">
-        <v>0</v>
-      </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
+      <c r="S60" s="3">
+        <v>0</v>
       </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
@@ -3933,8 +4073,11 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3981,11 +4124,11 @@
         <v>0</v>
       </c>
       <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>4900</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4001,8 +4144,11 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4013,10 +4159,10 @@
         <v>300</v>
       </c>
       <c r="F62" s="3">
+        <v>300</v>
+      </c>
+      <c r="G62" s="3">
         <v>1200</v>
-      </c>
-      <c r="G62" s="3">
-        <v>200</v>
       </c>
       <c r="H62" s="3">
         <v>200</v>
@@ -4046,11 +4192,11 @@
         <v>200</v>
       </c>
       <c r="Q62" s="3">
+        <v>200</v>
+      </c>
+      <c r="R62" s="3">
         <v>400</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4069,8 +4215,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4137,8 +4286,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4205,8 +4357,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4273,59 +4428,62 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E66" s="3">
         <v>3500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>800</v>
-      </c>
-      <c r="L66" s="3">
-        <v>1000</v>
       </c>
       <c r="M66" s="3">
         <v>1000</v>
       </c>
       <c r="N66" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O66" s="3">
         <v>900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>6800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5000</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4341,8 +4499,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4367,8 +4528,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4435,8 +4597,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4503,8 +4668,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4548,13 +4716,13 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
-        <v>6600</v>
+        <v>0</v>
       </c>
       <c r="R70" s="3">
         <v>6600</v>
       </c>
       <c r="S70" s="3">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="T70" s="3">
         <v>0</v>
@@ -4571,8 +4739,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4639,59 +4810,62 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-54700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-47400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-41900</v>
-      </c>
-      <c r="F72" s="3">
-        <v>-37000</v>
       </c>
       <c r="G72" s="3">
         <v>-37000</v>
       </c>
       <c r="H72" s="3">
+        <v>-37000</v>
+      </c>
+      <c r="I72" s="3">
         <v>-34800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-32500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-29400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-27200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-25400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-23700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-22000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-20200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-18500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-12400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-11600</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4707,8 +4881,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4775,8 +4952,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4843,8 +5023,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4911,59 +5094,62 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>15200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>16700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>18100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>20400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-12200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-11500</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4979,8 +5165,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5047,70 +5236,73 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43830</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43646</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43465</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43281</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5120,65 +5312,68 @@
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-4900</v>
       </c>
-      <c r="F81" s="3">
-        <v>0</v>
-      </c>
       <c r="G81" s="3">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3">
         <v>-2200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1800</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-1700</v>
       </c>
       <c r="M81" s="3">
         <v>-1700</v>
       </c>
       <c r="N81" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="O81" s="3">
         <v>-1800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-900</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5188,8 +5383,11 @@
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5214,8 +5412,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5258,8 +5457,8 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
+      <c r="Q83" s="3">
+        <v>0</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
@@ -5276,14 +5475,17 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W83" s="3">
-        <v>0</v>
+      <c r="W83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5350,8 +5552,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5418,8 +5623,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5486,8 +5694,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5554,8 +5765,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5622,59 +5836,62 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1200</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-2000</v>
       </c>
       <c r="H89" s="3">
         <v>-2000</v>
       </c>
       <c r="I89" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J89" s="3">
         <v>-2900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R89" s="3">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3">
         <v>-200</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5690,8 +5907,11 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5716,8 +5936,9 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5760,8 +5981,8 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
@@ -5778,14 +5999,17 @@
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
+      <c r="W91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5852,8 +6076,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5920,8 +6147,11 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5929,26 +6159,26 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>1000</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-1000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>6000</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-6000</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
         <v>0</v>
       </c>
@@ -5964,14 +6194,14 @@
       <c r="P94" s="3">
         <v>0</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3">
+        <v>0</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
@@ -5982,14 +6212,17 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
+      <c r="W94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6014,8 +6247,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6082,8 +6316,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6150,8 +6387,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6218,8 +6458,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6286,20 +6529,23 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E100" s="3">
+      <c r="E100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F100" s="3">
         <v>1000</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6318,27 +6564,27 @@
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>1900</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>5600</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R100" s="3">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3">
         <v>200</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6354,16 +6600,19 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F101" s="3">
         <v>0</v>
@@ -6374,8 +6623,8 @@
       <c r="H101" s="3">
         <v>0</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
+      <c r="I101" s="3">
+        <v>0</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
@@ -6383,14 +6632,14 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
@@ -6422,58 +6671,61 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>4000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-6900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>3700</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3">
+        <v>0</v>
       </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
@@ -6488,6 +6740,9 @@
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PRFX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PRFX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="92">
   <si>
     <t>PRFX</t>
   </si>
@@ -769,23 +769,23 @@
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -1148,26 +1148,26 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1385,8 +1385,8 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-7300</v>
       </c>
       <c r="E18" s="3">
         <v>-5600</v>
@@ -1483,26 +1483,26 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G20" s="3">
         <v>-1300</v>
       </c>
-      <c r="G20" s="3">
-        <v>1400</v>
-      </c>
       <c r="H20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1554,23 +1554,23 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-7300</v>
       </c>
       <c r="E21" s="3">
-        <v>-5500</v>
+        <v>-5600</v>
       </c>
       <c r="F21" s="3">
-        <v>-4900</v>
+        <v>-5000</v>
       </c>
       <c r="G21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H21" s="3">
-        <v>-2200</v>
+        <v>-2300</v>
       </c>
       <c r="I21" s="3">
-        <v>-2300</v>
+        <v>-2400</v>
       </c>
       <c r="J21" s="3">
         <v>-3200</v>
@@ -1625,26 +1625,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2335,26 +2335,26 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="G32" s="3">
         <v>1300</v>
       </c>
-      <c r="G32" s="3">
-        <v>-1400</v>
-      </c>
       <c r="H32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -2830,16 +2830,16 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>6100</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -2891,26 +2891,26 @@
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F43" s="3">
         <v>0</v>
       </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2962,26 +2962,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3033,26 +3033,26 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>200</v>
-      </c>
-      <c r="E45" s="3">
-        <v>900</v>
-      </c>
-      <c r="F45" s="3">
-        <v>1800</v>
-      </c>
-      <c r="G45" s="3">
-        <v>3200</v>
-      </c>
-      <c r="H45" s="3">
-        <v>3100</v>
-      </c>
-      <c r="I45" s="3">
-        <v>2200</v>
-      </c>
-      <c r="J45" s="3">
-        <v>8200</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K45" s="3">
         <v>7900</v>
@@ -3175,26 +3175,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3530,26 +3530,26 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -3869,16 +3869,16 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -3939,26 +3939,26 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>4800</v>
-      </c>
-      <c r="E59" s="3">
-        <v>3000</v>
-      </c>
-      <c r="F59" s="3">
-        <v>2200</v>
-      </c>
-      <c r="G59" s="3">
-        <v>900</v>
-      </c>
-      <c r="H59" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I59" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J59" s="3">
-        <v>900</v>
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K59" s="3">
         <v>800</v>
@@ -4162,7 +4162,7 @@
         <v>300</v>
       </c>
       <c r="G62" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="H62" s="3">
         <v>200</v>
@@ -5954,11 +5954,11 @@
       <c r="G91" s="3">
         <v>0</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -6253,26 +6253,26 @@
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6537,8 +6537,8 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3">
+        <v>3400</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>3</v>
@@ -6546,8 +6546,8 @@
       <c r="F100" s="3">
         <v>1000</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
+      <c r="G100" s="3">
+        <v>3600</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>3</v>
@@ -6608,17 +6608,17 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
+      <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H101" s="3">
         <v>0</v>

--- a/AAII_Financials/Quarterly/PRFX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PRFX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="92">
   <si>
     <t>PRFX</t>
   </si>
@@ -656,113 +656,120 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43465</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43281</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -787,11 +794,11 @@
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -832,8 +839,14 @@
       <c r="Y8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -903,8 +916,14 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -974,8 +993,14 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1001,79 +1026,87 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>100</v>
+      </c>
+      <c r="E12" s="3">
+        <v>100</v>
+      </c>
+      <c r="F12" s="3">
         <v>6700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>4700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>2700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>1200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>1500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>1900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>1100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>1000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>100</v>
       </c>
-      <c r="S12" s="3">
-        <v>0</v>
-      </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
+        <v>0</v>
+      </c>
+      <c r="V12" s="3">
         <v>200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>100</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1143,8 +1176,14 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1169,11 +1208,11 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1214,8 +1253,14 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1285,8 +1330,14 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1309,150 +1360,164 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>900</v>
+      </c>
+      <c r="E17" s="3">
+        <v>900</v>
+      </c>
+      <c r="F17" s="3">
         <v>7300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>5600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>3600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>2300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>2400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>3300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>2100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1700</v>
-      </c>
-      <c r="N17" s="3">
-        <v>1700</v>
-      </c>
-      <c r="O17" s="3">
-        <v>1800</v>
       </c>
       <c r="P17" s="3">
         <v>1700</v>
       </c>
       <c r="Q17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="R17" s="3">
+        <v>1700</v>
+      </c>
+      <c r="S17" s="3">
         <v>2000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>300</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-7300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-5600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-3600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-1400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-2300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-2400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-3300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-2100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-1800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-1700</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-1800</v>
       </c>
       <c r="P18" s="3">
         <v>-1700</v>
       </c>
       <c r="Q18" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="R18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="S18" s="3">
         <v>-2000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-300</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1478,8 +1543,10 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1490,17 +1557,17 @@
         <v>0</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>1400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-1300</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
@@ -1526,22 +1593,22 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-600</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-300</v>
       </c>
       <c r="U20" s="3">
         <v>-200</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
+      <c r="V20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="W20" s="3">
+        <v>-200</v>
       </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
@@ -1549,59 +1616,65 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F21" s="3">
         <v>-7300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-5600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-5000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-2300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-2400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-3200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-2100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-1800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-1700</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-1800</v>
       </c>
       <c r="P21" s="3">
         <v>-1700</v>
       </c>
       <c r="Q21" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="R21" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="S21" s="3">
         <v>-2000</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1620,8 +1693,14 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1646,11 +1725,11 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1691,70 +1770,76 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F23" s="3">
         <v>-7300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-5500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-4900</v>
       </c>
-      <c r="G23" s="3">
-        <v>0</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
         <v>-2200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-2300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-3200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-2100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-1800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-1700</v>
-      </c>
-      <c r="N23" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="O23" s="3">
-        <v>-1800</v>
       </c>
       <c r="P23" s="3">
         <v>-1700</v>
       </c>
       <c r="Q23" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="R23" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="S23" s="3">
         <v>-2000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-1300</v>
-      </c>
-      <c r="S23" s="3">
-        <v>-400</v>
-      </c>
-      <c r="T23" s="3">
-        <v>-800</v>
       </c>
       <c r="U23" s="3">
         <v>-400</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
+      <c r="V23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="W23" s="3">
+        <v>-400</v>
       </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
@@ -1762,49 +1847,55 @@
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
+      <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
+      <c r="H24" s="3">
+        <v>0</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
+      <c r="L24" s="3">
+        <v>0</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
+      <c r="N24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
+      <c r="P24" s="3">
+        <v>0</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
@@ -1818,11 +1909,11 @@
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
-      <c r="V24" s="3">
-        <v>0</v>
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
@@ -1833,8 +1924,14 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1904,70 +2001,76 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F26" s="3">
         <v>-7300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-5500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-4900</v>
       </c>
-      <c r="G26" s="3">
-        <v>0</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
         <v>-2200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-2300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-3200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-2100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-1800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-1700</v>
-      </c>
-      <c r="N26" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-1800</v>
       </c>
       <c r="P26" s="3">
         <v>-1700</v>
       </c>
       <c r="Q26" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="R26" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="S26" s="3">
         <v>-2000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-1300</v>
-      </c>
-      <c r="S26" s="3">
-        <v>-400</v>
-      </c>
-      <c r="T26" s="3">
-        <v>-800</v>
       </c>
       <c r="U26" s="3">
         <v>-400</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
+      <c r="V26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="W26" s="3">
+        <v>-400</v>
       </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
@@ -1975,79 +2078,91 @@
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F27" s="3">
         <v>-7300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-5500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-4900</v>
       </c>
-      <c r="G27" s="3">
-        <v>0</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3">
         <v>-2200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-2300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-3200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-2100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-1800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-1700</v>
-      </c>
-      <c r="N27" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-1800</v>
       </c>
       <c r="P27" s="3">
         <v>-1700</v>
       </c>
       <c r="Q27" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="R27" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="S27" s="3">
         <v>-2000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-2400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-1000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-1900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-900</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2117,8 +2232,14 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2188,8 +2309,14 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2259,8 +2386,14 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2330,8 +2463,14 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2342,17 +2481,17 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-1400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>1300</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
@@ -2378,22 +2517,22 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>600</v>
-      </c>
-      <c r="S32" s="3">
-        <v>200</v>
-      </c>
-      <c r="T32" s="3">
-        <v>300</v>
       </c>
       <c r="U32" s="3">
         <v>200</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
+      <c r="V32" s="3">
+        <v>300</v>
+      </c>
+      <c r="W32" s="3">
+        <v>200</v>
       </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
@@ -2401,79 +2540,91 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F33" s="3">
         <v>-7300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-5500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-4900</v>
       </c>
-      <c r="G33" s="3">
-        <v>0</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3">
         <v>-2200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-2300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-3200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-2100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-1800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-1700</v>
-      </c>
-      <c r="N33" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="O33" s="3">
-        <v>-1800</v>
       </c>
       <c r="P33" s="3">
         <v>-1700</v>
       </c>
       <c r="Q33" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="R33" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="S33" s="3">
         <v>-2000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-2400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-1000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-1900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-900</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2543,155 +2694,173 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F35" s="3">
         <v>-7300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-5500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-4900</v>
       </c>
-      <c r="G35" s="3">
-        <v>0</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3">
         <v>-2200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-2300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-3200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-2100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-1800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-1700</v>
-      </c>
-      <c r="N35" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="O35" s="3">
-        <v>-1800</v>
       </c>
       <c r="P35" s="3">
         <v>-1700</v>
       </c>
       <c r="Q35" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="R35" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="S35" s="3">
         <v>-2000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-2400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-1000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-1900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-900</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43465</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43281</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2717,8 +2886,10 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2744,65 +2915,67 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2800</v>
+        <v>4300</v>
       </c>
       <c r="E41" s="3">
         <v>4300</v>
       </c>
       <c r="F41" s="3">
+        <v>2800</v>
+      </c>
+      <c r="G41" s="3">
+        <v>4300</v>
+      </c>
+      <c r="H41" s="3">
         <v>8000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>7600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>5100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>8100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>4100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>6900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>13800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>15400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>16500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>18300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>17800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>19400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>100</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2815,8 +2988,14 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2830,23 +3009,23 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>1000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>1000</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>6100</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -2886,38 +3065,44 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
+      <c r="D43" s="3">
+        <v>100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>100</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
+      <c r="H43" s="3">
+        <v>0</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J43" s="3">
+      <c r="J43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L43" s="3">
         <v>100</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
       <c r="M43" s="3">
         <v>0</v>
       </c>
@@ -2957,8 +3142,14 @@
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2983,11 +3174,11 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3028,8 +3219,14 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3054,38 +3251,38 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>7900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>2100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>2200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>2500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>2000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>2000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>1900</v>
       </c>
-      <c r="R45" s="3">
-        <v>0</v>
-      </c>
-      <c r="S45" s="3">
-        <v>0</v>
-      </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
+      <c r="T45" s="3">
+        <v>0</v>
+      </c>
+      <c r="U45" s="3">
+        <v>0</v>
       </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
@@ -3099,65 +3296,71 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F46" s="3">
         <v>3000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>5200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>9800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>10700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>8300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>10400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>12300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>14800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>15900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>17700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>19000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>20300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>19800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>21300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>1000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>100</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3170,8 +3373,14 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3196,11 +3405,11 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3241,8 +3450,14 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3259,10 +3474,10 @@
         <v>100</v>
       </c>
       <c r="H48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J48" s="3">
         <v>0</v>
@@ -3271,25 +3486,25 @@
         <v>0</v>
       </c>
       <c r="L48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3">
         <v>100</v>
       </c>
       <c r="O48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q48" s="3">
         <v>0</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
+      <c r="R48" s="3">
+        <v>0</v>
       </c>
       <c r="S48" s="3">
         <v>0</v>
@@ -3297,8 +3512,8 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
+      <c r="U48" s="3">
+        <v>0</v>
       </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
@@ -3312,8 +3527,14 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3383,8 +3604,14 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3454,8 +3681,14 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3525,8 +3758,14 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3551,11 +3790,11 @@
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -3566,21 +3805,21 @@
       <c r="O52" s="3">
         <v>0</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R52" s="3">
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T52" s="3">
         <v>200</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3596,8 +3835,14 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3667,65 +3912,71 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>4500</v>
+      </c>
+      <c r="F54" s="3">
         <v>3100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>5400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>9900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>10900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>8300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>10400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>12300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>14900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>16000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>17700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>19100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>20300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>19800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>21400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>1200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>100</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3738,8 +3989,14 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3765,8 +4022,10 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3792,46 +4051,48 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>300</v>
+      </c>
+      <c r="F57" s="3">
         <v>100</v>
-      </c>
-      <c r="E57" s="3">
-        <v>200</v>
-      </c>
-      <c r="F57" s="3">
-        <v>200</v>
       </c>
       <c r="G57" s="3">
         <v>200</v>
       </c>
       <c r="H57" s="3">
+        <v>200</v>
+      </c>
+      <c r="I57" s="3">
+        <v>200</v>
+      </c>
+      <c r="J57" s="3">
         <v>100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>300</v>
-      </c>
-      <c r="J57" s="3">
-        <v>200</v>
-      </c>
-      <c r="K57" s="3">
-        <v>400</v>
       </c>
       <c r="L57" s="3">
         <v>200</v>
       </c>
       <c r="M57" s="3">
+        <v>400</v>
+      </c>
+      <c r="N57" s="3">
+        <v>200</v>
+      </c>
+      <c r="O57" s="3">
         <v>300</v>
-      </c>
-      <c r="N57" s="3">
-        <v>100</v>
-      </c>
-      <c r="O57" s="3">
-        <v>200</v>
       </c>
       <c r="P57" s="3">
         <v>100</v>
@@ -3839,11 +4100,11 @@
       <c r="Q57" s="3">
         <v>200</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
+      <c r="R57" s="3">
+        <v>100</v>
+      </c>
+      <c r="S57" s="3">
+        <v>200</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
@@ -3857,22 +4118,28 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X57" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F58" s="3">
         <v>100</v>
@@ -3881,10 +4148,10 @@
         <v>100</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
@@ -3904,21 +4171,21 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R58" s="3">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T58" s="3">
         <v>6200</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3934,8 +4201,14 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3960,38 +4233,38 @@
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3">
         <v>800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>400</v>
-      </c>
-      <c r="N59" s="3">
-        <v>600</v>
-      </c>
-      <c r="O59" s="3">
-        <v>500</v>
       </c>
       <c r="P59" s="3">
         <v>600</v>
       </c>
       <c r="Q59" s="3">
+        <v>500</v>
+      </c>
+      <c r="R59" s="3">
         <v>600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
+        <v>600</v>
+      </c>
+      <c r="T59" s="3">
         <v>200</v>
       </c>
-      <c r="S59" s="3">
-        <v>0</v>
-      </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
+      <c r="U59" s="3">
+        <v>0</v>
       </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
@@ -4005,64 +4278,70 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F60" s="3">
         <v>4900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>3300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1100</v>
-      </c>
-      <c r="H60" s="3">
-        <v>1100</v>
-      </c>
-      <c r="I60" s="3">
-        <v>1300</v>
       </c>
       <c r="J60" s="3">
         <v>1100</v>
       </c>
       <c r="K60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L60" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M60" s="3">
         <v>1200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>6300</v>
       </c>
-      <c r="S60" s="3">
-        <v>0</v>
-      </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
+      <c r="U60" s="3">
+        <v>0</v>
       </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
@@ -4076,8 +4355,14 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4127,14 +4412,14 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
         <v>4900</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4147,8 +4432,14 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4162,13 +4453,13 @@
         <v>300</v>
       </c>
       <c r="G62" s="3">
+        <v>300</v>
+      </c>
+      <c r="H62" s="3">
+        <v>300</v>
+      </c>
+      <c r="I62" s="3">
         <v>1100</v>
-      </c>
-      <c r="H62" s="3">
-        <v>200</v>
-      </c>
-      <c r="I62" s="3">
-        <v>200</v>
       </c>
       <c r="J62" s="3">
         <v>200</v>
@@ -4195,14 +4486,14 @@
         <v>200</v>
       </c>
       <c r="R62" s="3">
+        <v>200</v>
+      </c>
+      <c r="S62" s="3">
+        <v>200</v>
+      </c>
+      <c r="T62" s="3">
         <v>400</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4218,8 +4509,14 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4289,8 +4586,14 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4360,8 +4663,14 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4431,65 +4740,71 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F66" s="3">
         <v>5100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>3500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>2700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>2200</v>
-      </c>
-      <c r="H66" s="3">
-        <v>1300</v>
-      </c>
-      <c r="I66" s="3">
-        <v>1500</v>
       </c>
       <c r="J66" s="3">
         <v>1300</v>
       </c>
       <c r="K66" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="M66" s="3">
         <v>1400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>6800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>5000</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4502,8 +4817,14 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4529,8 +4850,10 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4600,8 +4923,14 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4671,8 +5000,14 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4719,17 +5054,17 @@
         <v>0</v>
       </c>
       <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
         <v>6600</v>
       </c>
-      <c r="S70" s="3">
+      <c r="U70" s="3">
         <v>6600</v>
       </c>
-      <c r="T70" s="3">
-        <v>0</v>
-      </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
       <c r="V70" s="3">
         <v>0</v>
       </c>
@@ -4742,8 +5077,14 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4813,65 +5154,71 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-56500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-56500</v>
+      </c>
+      <c r="F72" s="3">
         <v>-54700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-47400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-41900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-37000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-37000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-34800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-32500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-29400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-27200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-25400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-23700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-22000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-20200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-18500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-12400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-11600</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4884,8 +5231,14 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4955,8 +5308,14 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5026,8 +5385,14 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5097,65 +5462,71 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-2000</v>
+        <v>1800</v>
       </c>
       <c r="E76" s="3">
         <v>1800</v>
       </c>
       <c r="F76" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="G76" s="3">
+        <v>1800</v>
+      </c>
+      <c r="H76" s="3">
         <v>7200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>8600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>7000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>8900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>11000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>13400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>15200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>16700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>18100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>19500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>19000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>20400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>-12200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>-11500</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5168,8 +5539,14 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5239,155 +5616,173 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43465</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43281</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F81" s="3">
         <v>-7300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-5500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-4900</v>
       </c>
-      <c r="G81" s="3">
-        <v>0</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3">
         <v>-2200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-2300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-3200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-2100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-1800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-1700</v>
-      </c>
-      <c r="N81" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="O81" s="3">
-        <v>-1800</v>
       </c>
       <c r="P81" s="3">
         <v>-1700</v>
       </c>
       <c r="Q81" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="R81" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="S81" s="3">
         <v>-2000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-2400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-1000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-1900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-900</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5413,8 +5808,10 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5460,11 +5857,11 @@
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+      <c r="S83" s="3">
+        <v>0</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
@@ -5478,14 +5875,20 @@
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X83" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5555,8 +5958,14 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5626,8 +6035,14 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5697,8 +6112,14 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5768,8 +6189,14 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5839,65 +6266,71 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F89" s="3">
         <v>-4900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-3700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-1600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-1200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-2000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-2000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-2900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-1600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-1100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-1800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-1400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-1800</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U89" s="3">
         <v>-200</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5910,8 +6343,14 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5937,8 +6376,10 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5954,17 +6395,17 @@
       <c r="G91" s="3">
         <v>0</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -5984,11 +6425,11 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
@@ -6002,14 +6443,20 @@
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6079,8 +6526,14 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6150,8 +6603,14 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6162,29 +6621,29 @@
         <v>0</v>
       </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>1000</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-1000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>6000</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-6000</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
@@ -6197,8 +6656,8 @@
       <c r="Q94" s="3">
         <v>0</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
+      <c r="R94" s="3">
+        <v>0</v>
       </c>
       <c r="S94" s="3">
         <v>0</v>
@@ -6206,8 +6665,8 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
+      <c r="U94" s="3">
+        <v>0</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
@@ -6215,14 +6674,20 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6248,8 +6713,10 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6274,11 +6741,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6319,8 +6786,14 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6390,8 +6863,14 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6461,8 +6940,14 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6532,29 +7017,35 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E100" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F100" s="3">
         <v>3400</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3">
         <v>1000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>3600</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6567,30 +7058,30 @@
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>1900</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>5600</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U100" s="3">
         <v>200</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6603,8 +7094,14 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6614,29 +7111,29 @@
       <c r="E101" s="3">
         <v>0</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
+        <v>0</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
@@ -6644,8 +7141,8 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -6674,64 +7171,70 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>700</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-3700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>2400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-3000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>4000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-2800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-6900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-1600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-1100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-1800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>3700</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
+      <c r="U102" s="3">
+        <v>0</v>
       </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
@@ -6743,6 +7246,12 @@
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PRFX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PRFX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="92">
   <si>
     <t>PRFX</t>
   </si>
@@ -656,136 +656,143 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>3</v>
+      <c r="E8" s="3">
+        <v>0</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>3</v>
@@ -814,11 +821,11 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3">
-        <v>0</v>
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
@@ -859,16 +866,22 @@
       <c r="AC8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>3</v>
@@ -942,16 +955,22 @@
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>3</v>
@@ -1025,8 +1044,14 @@
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1056,16 +1081,18 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E12" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="F12" s="3">
         <v>100</v>
@@ -1074,73 +1101,79 @@
         <v>100</v>
       </c>
       <c r="H12" s="3">
+        <v>100</v>
+      </c>
+      <c r="I12" s="3">
+        <v>100</v>
+      </c>
+      <c r="J12" s="3">
         <v>6700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>4700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>2700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>1200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>1500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>1900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>1100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>1000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>100</v>
       </c>
-      <c r="W12" s="3">
-        <v>0</v>
-      </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="3">
         <v>200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>100</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1222,8 +1255,14 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1260,11 +1299,11 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1305,23 +1344,29 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>300</v>
+      </c>
+      <c r="E15" s="3">
+        <v>300</v>
+      </c>
+      <c r="F15" s="3">
         <v>100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>100</v>
       </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
       <c r="H15" s="3">
         <v>0</v>
       </c>
@@ -1388,8 +1433,14 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1416,174 +1467,188 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F17" s="3">
         <v>1200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>7300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>5600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>3600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>2300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>2400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>3300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>2100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1700</v>
-      </c>
-      <c r="R17" s="3">
-        <v>1700</v>
-      </c>
-      <c r="S17" s="3">
-        <v>1800</v>
       </c>
       <c r="T17" s="3">
         <v>1700</v>
       </c>
       <c r="U17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="V17" s="3">
+        <v>1700</v>
+      </c>
+      <c r="W17" s="3">
         <v>2000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>300</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-1200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-7300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-5600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-3600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-1400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-2300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-2400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-3300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-2100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-1700</v>
-      </c>
-      <c r="R18" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="S18" s="3">
-        <v>-1800</v>
       </c>
       <c r="T18" s="3">
         <v>-1700</v>
       </c>
       <c r="U18" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="V18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="W18" s="3">
         <v>-2000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-300</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1613,8 +1678,10 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1637,17 +1704,17 @@
         <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>1400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-1300</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
@@ -1673,22 +1740,22 @@
         <v>0</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>-600</v>
-      </c>
-      <c r="W20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="X20" s="3">
-        <v>-300</v>
       </c>
       <c r="Y20" s="3">
         <v>-200</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
+      <c r="Z20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>-200</v>
       </c>
       <c r="AB20" s="3" t="s">
         <v>3</v>
@@ -1696,8 +1763,14 @@
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1708,59 +1781,59 @@
         <v>-1100</v>
       </c>
       <c r="F21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="H21" s="3">
         <v>-900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-7300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-5600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-5000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-2300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-2400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-3200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-2100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-1700</v>
-      </c>
-      <c r="R21" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="S21" s="3">
-        <v>-1800</v>
       </c>
       <c r="T21" s="3">
         <v>-1700</v>
       </c>
       <c r="U21" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="V21" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="W21" s="3">
         <v>-2000</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1779,8 +1852,14 @@
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1817,11 +1896,11 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1862,82 +1941,88 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-7300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-5500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-4900</v>
       </c>
-      <c r="K23" s="3">
-        <v>0</v>
-      </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3">
         <v>-2200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-2300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-3200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-2100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-1700</v>
-      </c>
-      <c r="R23" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="S23" s="3">
-        <v>-1800</v>
       </c>
       <c r="T23" s="3">
         <v>-1700</v>
       </c>
       <c r="U23" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="V23" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="W23" s="3">
         <v>-2000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-1300</v>
-      </c>
-      <c r="W23" s="3">
-        <v>-400</v>
-      </c>
-      <c r="X23" s="3">
-        <v>-800</v>
       </c>
       <c r="Y23" s="3">
         <v>-400</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
+      <c r="Z23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AA23" s="3">
+        <v>-400</v>
       </c>
       <c r="AB23" s="3" t="s">
         <v>3</v>
@@ -1945,61 +2030,67 @@
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
+      <c r="L24" s="3">
+        <v>0</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
+      <c r="N24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
+      <c r="P24" s="3">
+        <v>0</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
+      <c r="T24" s="3">
+        <v>0</v>
       </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
@@ -2013,11 +2104,11 @@
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>0</v>
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA24" s="3">
         <v>0</v>
@@ -2028,8 +2119,14 @@
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2111,82 +2208,88 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-7300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-5500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-4900</v>
       </c>
-      <c r="K26" s="3">
-        <v>0</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
+        <v>0</v>
+      </c>
+      <c r="N26" s="3">
         <v>-2200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-2300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-3200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-2100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-1700</v>
-      </c>
-      <c r="R26" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="S26" s="3">
-        <v>-1800</v>
       </c>
       <c r="T26" s="3">
         <v>-1700</v>
       </c>
       <c r="U26" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="V26" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="W26" s="3">
         <v>-2000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-1300</v>
-      </c>
-      <c r="W26" s="3">
-        <v>-400</v>
-      </c>
-      <c r="X26" s="3">
-        <v>-800</v>
       </c>
       <c r="Y26" s="3">
         <v>-400</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
+      <c r="Z26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AA26" s="3">
+        <v>-400</v>
       </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
@@ -2194,91 +2297,103 @@
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-7300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-5500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-4900</v>
       </c>
-      <c r="K27" s="3">
-        <v>0</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
+        <v>0</v>
+      </c>
+      <c r="N27" s="3">
         <v>-2200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-2300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-3200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-2100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-1700</v>
-      </c>
-      <c r="R27" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="S27" s="3">
-        <v>-1800</v>
       </c>
       <c r="T27" s="3">
         <v>-1700</v>
       </c>
       <c r="U27" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="V27" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="W27" s="3">
         <v>-2000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-2400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-1000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-900</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2360,8 +2475,14 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2443,8 +2564,14 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2526,8 +2653,14 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2609,8 +2742,14 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2633,17 +2772,17 @@
         <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-1400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>1300</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
@@ -2669,22 +2808,22 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>600</v>
-      </c>
-      <c r="W32" s="3">
-        <v>200</v>
-      </c>
-      <c r="X32" s="3">
-        <v>300</v>
       </c>
       <c r="Y32" s="3">
         <v>200</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
+      <c r="Z32" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>200</v>
       </c>
       <c r="AB32" s="3" t="s">
         <v>3</v>
@@ -2692,91 +2831,103 @@
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-1200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-7300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-5500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-4900</v>
       </c>
-      <c r="K33" s="3">
-        <v>0</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3">
         <v>-2200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-2300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-3200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-2100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-1700</v>
-      </c>
-      <c r="R33" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="S33" s="3">
-        <v>-1800</v>
       </c>
       <c r="T33" s="3">
         <v>-1700</v>
       </c>
       <c r="U33" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="V33" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="W33" s="3">
         <v>-2000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-2400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-1000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-900</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2858,179 +3009,197 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-1200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-7300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-5500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-4900</v>
       </c>
-      <c r="K35" s="3">
-        <v>0</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
+        <v>0</v>
+      </c>
+      <c r="N35" s="3">
         <v>-2200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-2300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-3200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-2100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-1700</v>
-      </c>
-      <c r="R35" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="S35" s="3">
-        <v>-1800</v>
       </c>
       <c r="T35" s="3">
         <v>-1700</v>
       </c>
       <c r="U35" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="V35" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="W35" s="3">
         <v>-2000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-2400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-1000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-900</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3060,8 +3229,10 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3091,77 +3262,79 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F41" s="3">
         <v>3500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>3500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>4300</v>
-      </c>
-      <c r="G41" s="3">
-        <v>4300</v>
-      </c>
-      <c r="H41" s="3">
-        <v>2800</v>
       </c>
       <c r="I41" s="3">
         <v>4300</v>
       </c>
       <c r="J41" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K41" s="3">
+        <v>4300</v>
+      </c>
+      <c r="L41" s="3">
         <v>8000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>7600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>5100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>8100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>4100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>6900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>13800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>15400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>16500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>18300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>17800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>19400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>100</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3174,16 +3347,22 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -3201,23 +3380,23 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>1000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>1000</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>6100</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -3257,50 +3436,56 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>100</v>
+      </c>
+      <c r="F43" s="3">
         <v>300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>100</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
+      <c r="L43" s="3">
+        <v>0</v>
       </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="3">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3">
         <v>100</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
       <c r="Q43" s="3">
         <v>0</v>
       </c>
@@ -3340,8 +3525,14 @@
       <c r="AC43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3378,11 +3569,11 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3423,16 +3614,22 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
@@ -3461,38 +3658,38 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>7900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>2100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>2200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>2500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>2000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>2000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>1900</v>
       </c>
-      <c r="V45" s="3">
-        <v>0</v>
-      </c>
-      <c r="W45" s="3">
-        <v>0</v>
-      </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
+      <c r="X45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
+        <v>0</v>
       </c>
       <c r="Z45" s="3" t="s">
         <v>3</v>
@@ -3506,77 +3703,83 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F46" s="3">
         <v>3900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>3900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>4400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>4400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>3000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>5200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>9800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>10700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>8300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>10400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>12300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>14800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>15900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>17700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>19000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>20300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>19800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>21300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>1000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>100</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3589,8 +3792,14 @@
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3627,11 +3836,11 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3672,8 +3881,14 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3702,10 +3917,10 @@
         <v>100</v>
       </c>
       <c r="L48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N48" s="3">
         <v>0</v>
@@ -3714,25 +3929,25 @@
         <v>0</v>
       </c>
       <c r="P48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R48" s="3">
         <v>100</v>
       </c>
       <c r="S48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U48" s="3">
         <v>0</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
+      <c r="V48" s="3">
+        <v>0</v>
       </c>
       <c r="W48" s="3">
         <v>0</v>
@@ -3740,8 +3955,8 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
+      <c r="Y48" s="3">
+        <v>0</v>
       </c>
       <c r="Z48" s="3" t="s">
         <v>3</v>
@@ -3755,23 +3970,29 @@
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E49" s="3">
+        <v>7600</v>
+      </c>
+      <c r="F49" s="3">
         <v>7100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>7100</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
       <c r="H49" s="3">
         <v>0</v>
       </c>
@@ -3838,8 +4059,14 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3921,8 +4148,14 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4004,8 +4237,14 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4042,11 +4281,11 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
-      <c r="P52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q52" s="3">
         <v>0</v>
@@ -4057,21 +4296,21 @@
       <c r="S52" s="3">
         <v>0</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V52" s="3">
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X52" s="3">
         <v>200</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4087,8 +4326,14 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4170,77 +4415,83 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>12000</v>
+      </c>
+      <c r="F54" s="3">
         <v>11200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>11200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>4500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>4500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>3100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>5400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>9900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>10900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>8300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>10400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>12300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>14900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>16000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>17700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>19100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>20300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>19800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>21400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>1200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>100</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4253,8 +4504,14 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4284,8 +4541,10 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4315,8 +4574,10 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4327,46 +4588,46 @@
         <v>200</v>
       </c>
       <c r="F57" s="3">
+        <v>200</v>
+      </c>
+      <c r="G57" s="3">
+        <v>200</v>
+      </c>
+      <c r="H57" s="3">
         <v>300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>100</v>
-      </c>
-      <c r="I57" s="3">
-        <v>200</v>
-      </c>
-      <c r="J57" s="3">
-        <v>200</v>
       </c>
       <c r="K57" s="3">
         <v>200</v>
       </c>
       <c r="L57" s="3">
+        <v>200</v>
+      </c>
+      <c r="M57" s="3">
+        <v>200</v>
+      </c>
+      <c r="N57" s="3">
         <v>100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>300</v>
-      </c>
-      <c r="N57" s="3">
-        <v>200</v>
-      </c>
-      <c r="O57" s="3">
-        <v>400</v>
       </c>
       <c r="P57" s="3">
         <v>200</v>
       </c>
       <c r="Q57" s="3">
+        <v>400</v>
+      </c>
+      <c r="R57" s="3">
+        <v>200</v>
+      </c>
+      <c r="S57" s="3">
         <v>300</v>
-      </c>
-      <c r="R57" s="3">
-        <v>100</v>
-      </c>
-      <c r="S57" s="3">
-        <v>200</v>
       </c>
       <c r="T57" s="3">
         <v>100</v>
@@ -4374,11 +4635,11 @@
       <c r="U57" s="3">
         <v>200</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
+      <c r="V57" s="3">
+        <v>100</v>
+      </c>
+      <c r="W57" s="3">
+        <v>200</v>
       </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
@@ -4392,34 +4653,40 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB57" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC57" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>100</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J58" s="3">
         <v>100</v>
@@ -4428,10 +4695,10 @@
         <v>100</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -4451,21 +4718,21 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V58" s="3">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X58" s="3">
         <v>6200</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4481,8 +4748,14 @@
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4519,38 +4792,38 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3">
         <v>800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>400</v>
-      </c>
-      <c r="R59" s="3">
-        <v>600</v>
-      </c>
-      <c r="S59" s="3">
-        <v>500</v>
       </c>
       <c r="T59" s="3">
         <v>600</v>
       </c>
       <c r="U59" s="3">
+        <v>500</v>
+      </c>
+      <c r="V59" s="3">
         <v>600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
+        <v>600</v>
+      </c>
+      <c r="X59" s="3">
         <v>200</v>
       </c>
-      <c r="W59" s="3">
-        <v>0</v>
-      </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
+      <c r="Y59" s="3">
+        <v>0</v>
       </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
@@ -4564,76 +4837,82 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F60" s="3">
         <v>2500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>2500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>2400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>4900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>3300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1100</v>
-      </c>
-      <c r="L60" s="3">
-        <v>1100</v>
-      </c>
-      <c r="M60" s="3">
-        <v>1300</v>
       </c>
       <c r="N60" s="3">
         <v>1100</v>
       </c>
       <c r="O60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="P60" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Q60" s="3">
         <v>1200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>6300</v>
       </c>
-      <c r="W60" s="3">
-        <v>0</v>
-      </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
+      <c r="Y60" s="3">
+        <v>0</v>
       </c>
       <c r="Z60" s="3" t="s">
         <v>3</v>
@@ -4647,8 +4926,14 @@
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4710,14 +4995,14 @@
         <v>0</v>
       </c>
       <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
         <v>4900</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -4730,8 +5015,14 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4757,13 +5048,13 @@
         <v>300</v>
       </c>
       <c r="K62" s="3">
+        <v>300</v>
+      </c>
+      <c r="L62" s="3">
+        <v>300</v>
+      </c>
+      <c r="M62" s="3">
         <v>1100</v>
-      </c>
-      <c r="L62" s="3">
-        <v>200</v>
-      </c>
-      <c r="M62" s="3">
-        <v>200</v>
       </c>
       <c r="N62" s="3">
         <v>200</v>
@@ -4790,14 +5081,14 @@
         <v>200</v>
       </c>
       <c r="V62" s="3">
+        <v>200</v>
+      </c>
+      <c r="W62" s="3">
+        <v>200</v>
+      </c>
+      <c r="X62" s="3">
         <v>400</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4813,8 +5104,14 @@
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4896,8 +5193,14 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4979,8 +5282,14 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5062,8 +5371,14 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -5080,59 +5395,59 @@
         <v>2700</v>
       </c>
       <c r="H66" s="3">
+        <v>2700</v>
+      </c>
+      <c r="I66" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J66" s="3">
         <v>5100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>3500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>2700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>2200</v>
-      </c>
-      <c r="L66" s="3">
-        <v>1300</v>
-      </c>
-      <c r="M66" s="3">
-        <v>1500</v>
       </c>
       <c r="N66" s="3">
         <v>1300</v>
       </c>
       <c r="O66" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Q66" s="3">
         <v>1400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>6800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>5000</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5145,8 +5460,14 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5176,8 +5497,10 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5259,8 +5582,14 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5342,8 +5671,14 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5402,17 +5737,17 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
         <v>6600</v>
       </c>
-      <c r="W70" s="3">
+      <c r="Y70" s="3">
         <v>6600</v>
       </c>
-      <c r="X70" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y70" s="3">
-        <v>0</v>
-      </c>
       <c r="Z70" s="3">
         <v>0</v>
       </c>
@@ -5425,8 +5760,14 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5508,77 +5849,83 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-61300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-61300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-58800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-58800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-56500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-56500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-54700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-47400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-41900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-37000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-37000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-34800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-32500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-29400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-27200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-25400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-23700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-22000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-20200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-18500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-12400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-11600</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5591,8 +5938,14 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5674,8 +6027,14 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5757,8 +6116,14 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5840,77 +6205,83 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>8500</v>
+      </c>
+      <c r="F76" s="3">
         <v>8400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>8400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1800</v>
-      </c>
-      <c r="G76" s="3">
-        <v>1800</v>
-      </c>
-      <c r="H76" s="3">
-        <v>-2000</v>
       </c>
       <c r="I76" s="3">
         <v>1800</v>
       </c>
       <c r="J76" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="K76" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L76" s="3">
         <v>7200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>8600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>7000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>8900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>11000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>13400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>15200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>16700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>18100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>19500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>19000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>20400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>-12200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>-11500</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5923,8 +6294,14 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6006,179 +6383,197 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-1200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-7300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-5500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-4900</v>
       </c>
-      <c r="K81" s="3">
-        <v>0</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
+        <v>0</v>
+      </c>
+      <c r="N81" s="3">
         <v>-2200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-2300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-3200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-2100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-1700</v>
-      </c>
-      <c r="R81" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="S81" s="3">
-        <v>-1800</v>
       </c>
       <c r="T81" s="3">
         <v>-1700</v>
       </c>
       <c r="U81" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="V81" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="W81" s="3">
         <v>-2000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-2400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-1000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-900</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6208,8 +6603,10 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6267,11 +6664,11 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+      <c r="W83" s="3">
+        <v>0</v>
       </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
@@ -6285,14 +6682,20 @@
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB83" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6374,8 +6777,14 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6457,8 +6866,14 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6540,8 +6955,14 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6623,8 +7044,14 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6706,8 +7133,14 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6718,65 +7151,65 @@
         <v>-1000</v>
       </c>
       <c r="F89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="H89" s="3">
         <v>-2000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-2000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-4900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-3700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-1600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-2000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-2000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-2900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-1100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-1800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-1400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-1600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-1800</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-200</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6789,8 +7222,14 @@
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6820,22 +7259,24 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
+      <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -6849,17 +7290,17 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
@@ -6879,11 +7320,11 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
@@ -6897,14 +7338,20 @@
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6986,8 +7433,14 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7069,16 +7522,22 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>
@@ -7093,29 +7552,29 @@
         <v>0</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>1000</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-1000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>6000</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-6000</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
@@ -7128,8 +7587,8 @@
       <c r="U94" s="3">
         <v>0</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
+      <c r="V94" s="3">
+        <v>0</v>
       </c>
       <c r="W94" s="3">
         <v>0</v>
@@ -7137,8 +7596,8 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
+      <c r="Y94" s="3">
+        <v>0</v>
       </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
@@ -7146,14 +7605,20 @@
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7183,8 +7648,10 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7221,11 +7688,11 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7266,8 +7733,14 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7349,8 +7822,14 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7432,8 +7911,14 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7515,41 +8000,47 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E100" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F100" s="3">
         <v>600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>2700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>2700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>3400</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3">
         <v>1000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>3600</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7562,30 +8053,30 @@
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>1900</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>5600</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y100" s="3">
         <v>200</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7598,22 +8089,28 @@
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
         <v>0</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
+      <c r="E101" s="3">
+        <v>0</v>
       </c>
       <c r="F101" s="3">
         <v>0</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H101" s="3">
         <v>0</v>
@@ -7621,29 +8118,29 @@
       <c r="I101" s="3">
         <v>0</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
+      <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
@@ -7651,8 +8148,8 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
+      <c r="T101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
@@ -7681,76 +8178,82 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F102" s="3">
         <v>-400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-1500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-3700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>2400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-3000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>4000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-2800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-6900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-1100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-1800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-1600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>3700</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
+      <c r="Y102" s="3">
+        <v>0</v>
       </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
@@ -7762,6 +8265,12 @@
         <v>3</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
